--- a/devoluciones.xlsx
+++ b/devoluciones.xlsx
@@ -13,10 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="100">
-  <si>
-    <t>ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
   <si>
     <t>No.Factura</t>
   </si>
@@ -36,283 +33,109 @@
     <t>Fecha</t>
   </si>
   <si>
-    <t>5463452</t>
+    <t>34553</t>
   </si>
   <si>
     <t>Durman</t>
   </si>
   <si>
-    <t>Codo inyectado 1</t>
+    <t>Rodo</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>Defecto de fabricA</t>
-  </si>
-  <si>
-    <t>11/02/2025</t>
-  </si>
-  <si>
-    <t>435654</t>
-  </si>
-  <si>
-    <t>Codo inyectado 3</t>
-  </si>
-  <si>
-    <t>Defecto Fabrica</t>
-  </si>
-  <si>
-    <t>11/03/2025</t>
-  </si>
-  <si>
-    <t>546456</t>
-  </si>
-  <si>
-    <t>Trampa 2</t>
+    <t>wers</t>
+  </si>
+  <si>
+    <t>09/12/2025</t>
+  </si>
+  <si>
+    <t>445667</t>
+  </si>
+  <si>
+    <t>Dureco</t>
+  </si>
+  <si>
+    <t>Derts</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>Incompleto</t>
-  </si>
-  <si>
-    <t>10/06/2025</t>
-  </si>
-  <si>
-    <t>3453555</t>
-  </si>
-  <si>
-    <t>Codo</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Ninguno</t>
-  </si>
-  <si>
-    <t>09/07/2025</t>
-  </si>
-  <si>
-    <t>345345</t>
-  </si>
-  <si>
-    <t>red</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>erwe</t>
-  </si>
-  <si>
-    <t>04/01/2026</t>
-  </si>
-  <si>
-    <t>345664</t>
-  </si>
-  <si>
-    <t>La Mundial</t>
-  </si>
-  <si>
-    <t>Termo</t>
-  </si>
-  <si>
-    <t>Defecto de Fabrica</t>
-  </si>
-  <si>
-    <t>09/11/2021</t>
-  </si>
-  <si>
-    <t>345</t>
-  </si>
-  <si>
-    <t>La mundial</t>
-  </si>
-  <si>
-    <t>Bicicleta</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>producto no solucitado</t>
-  </si>
-  <si>
-    <t>13/05/2025</t>
-  </si>
-  <si>
-    <t>24432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Mundial </t>
-  </si>
-  <si>
-    <t>Rodo Naranja 2</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>23/02/2024</t>
-  </si>
-  <si>
-    <t>23423</t>
-  </si>
-  <si>
-    <t>Tinaco 1000L</t>
-  </si>
-  <si>
-    <t>Daño en transporte</t>
-  </si>
-  <si>
-    <t>06/03/2025</t>
-  </si>
-  <si>
-    <t>5645</t>
+    <t>Wos</t>
+  </si>
+  <si>
+    <t>07/10/2025</t>
+  </si>
+  <si>
+    <t>32456</t>
+  </si>
+  <si>
+    <t>rodo</t>
+  </si>
+  <si>
+    <t>fgh</t>
+  </si>
+  <si>
+    <t>xcfvg</t>
+  </si>
+  <si>
+    <t>12/08/2025</t>
+  </si>
+  <si>
+    <t>s33545</t>
+  </si>
+  <si>
+    <t>durman</t>
+  </si>
+  <si>
+    <t>Rodhf</t>
+  </si>
+  <si>
+    <t>sdfdsf</t>
+  </si>
+  <si>
+    <t>18/04/2025</t>
+  </si>
+  <si>
+    <t>643453</t>
   </si>
   <si>
     <t>Dewalt</t>
   </si>
   <si>
-    <t>Taladro</t>
-  </si>
-  <si>
-    <t>No trae su carbon</t>
-  </si>
-  <si>
-    <t>16/10/2024</t>
-  </si>
-  <si>
-    <t>63452</t>
-  </si>
-  <si>
-    <t>Tee</t>
-  </si>
-  <si>
-    <t>ere</t>
-  </si>
-  <si>
-    <t>11/03/2022</t>
-  </si>
-  <si>
-    <t>44534</t>
-  </si>
-  <si>
-    <t>Flote 1+1</t>
-  </si>
-  <si>
-    <t>Falto</t>
-  </si>
-  <si>
-    <t>11/03/2026</t>
-  </si>
-  <si>
-    <t>435345</t>
-  </si>
-  <si>
-    <t>Sherwin Williams</t>
-  </si>
-  <si>
-    <t>Pintura cubeta blanca</t>
-  </si>
-  <si>
-    <t>Producto Vencido</t>
-  </si>
-  <si>
-    <t>13/03/2025</t>
-  </si>
-  <si>
-    <t>2432</t>
-  </si>
-  <si>
-    <t>Tecnologica tls</t>
-  </si>
-  <si>
-    <t>Foco 40w</t>
-  </si>
-  <si>
-    <t>LLegaron quemados</t>
-  </si>
-  <si>
-    <t>07/11/2020</t>
-  </si>
-  <si>
-    <t>3454</t>
-  </si>
-  <si>
-    <t>RED BULL</t>
-  </si>
-  <si>
-    <t>latas</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>LlegARON APLASTADAS</t>
-  </si>
-  <si>
-    <t>12/03/2016</t>
-  </si>
-  <si>
-    <t>234343</t>
-  </si>
-  <si>
-    <t>Pinguino</t>
-  </si>
-  <si>
-    <t>Rodos de hielo</t>
-  </si>
-  <si>
-    <t>Se deritieron en el viaje</t>
-  </si>
-  <si>
-    <t>07/12/2018</t>
-  </si>
-  <si>
-    <t>Rodos de madera</t>
-  </si>
-  <si>
-    <t>Se pudrieron en el viaje</t>
-  </si>
-  <si>
-    <t>07/05/2021</t>
-  </si>
-  <si>
-    <t>345435</t>
-  </si>
-  <si>
-    <t>Codo de drenaje 4</t>
-  </si>
-  <si>
-    <t>Llegaron rotos</t>
-  </si>
-  <si>
-    <t>06/03/2021</t>
-  </si>
-  <si>
-    <t>34535</t>
-  </si>
-  <si>
-    <t>Caja plastica</t>
-  </si>
-  <si>
-    <t>Llegaron dañadas</t>
-  </si>
-  <si>
-    <t>11/01/2023</t>
-  </si>
-  <si>
-    <t>34234</t>
-  </si>
-  <si>
-    <t>Codo de media</t>
-  </si>
-  <si>
-    <t>09/10/2020</t>
+    <t>Demand</t>
+  </si>
+  <si>
+    <t>erea</t>
+  </si>
+  <si>
+    <t>07/01/2025</t>
+  </si>
+  <si>
+    <t>324324</t>
+  </si>
+  <si>
+    <t>Rebs</t>
+  </si>
+  <si>
+    <t>13/03/2024</t>
+  </si>
+  <si>
+    <t>12345678910</t>
+  </si>
+  <si>
+    <t>weressssssss</t>
+  </si>
+  <si>
+    <t>werete</t>
+  </si>
+  <si>
+    <t>dewalt</t>
+  </si>
+  <si>
+    <t>02/01/2025</t>
   </si>
 </sst>
 </file>
@@ -569,11 +392,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="3" max="3" customWidth="true" width="16.63"/>
-    <col min="7" max="7" customWidth="true" width="16.13"/>
+    <col min="2" max="2" customWidth="true" width="16.63"/>
+    <col min="6" max="6" customWidth="true" width="16.13"/>
     <col min="11" max="11" customWidth="true" width="14.38"/>
   </cols>
   <sheetData>
@@ -596,123 +419,66 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="G1" s="1"/>
     </row>
     <row r="2">
-      <c r="A2" t="n" s="0">
-        <v>3.0</v>
+      <c r="A2" t="s" s="0">
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>68</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>69</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n" s="0">
-        <v>4.0</v>
+      <c r="A3" t="s" s="0">
+        <v>33</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>85</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n" s="0">
-        <v>5.0</v>
+      <c r="A4" t="s" s="0">
+        <v>36</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>97</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>98</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>75</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>99</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
